--- a/Excel/Ejercicios/01- Datos.xlsx
+++ b/Excel/Ejercicios/01- Datos.xlsx
@@ -1,26 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nuria López Álvarez\Documents\Cursos impartidos\Excel y Power BI\Excel\Ejercicios\Soluciones\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\NURIA\EXCEL\Ejercicios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5FFD807-B5CB-4041-BDF7-F619D5152CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B733E89B-42B2-4CD1-864B-B186B8436245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-104" yWindow="-104" windowWidth="18640" windowHeight="9873" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-113" yWindow="-113" windowWidth="18257" windowHeight="10769" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Datos" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -228,14 +237,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="13.85"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.69921875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.7265625" style="1"/>
+    <col min="6" max="16384" width="8.69921875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
